--- a/Data/Raw/Council Tax.xlsx
+++ b/Data/Raw/Council Tax.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jabegu\Desktop\SQL\Principles-of-Data-Science-Coursework\Raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jabegu\Desktop\SQL\Principles-of-Data-Science-Coursework\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A06BCB2-9592-41E7-9CFE-EEC9C46BC8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E307A2E3-EF20-420C-8E01-4F8198D94689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{AAC90F36-24F6-4065-9BB2-86FA5D184E6E}"/>
   </bookViews>
@@ -639,7 +639,7 @@
         <v>3502.12</v>
       </c>
       <c r="H6" s="1">
-        <v>3502.12</v>
+        <v>4040.92</v>
       </c>
       <c r="I6" s="1">
         <v>4849.1000000000004</v>
